--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 04/front/export.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 04/front/export.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.56181</v>
+        <v>16.73974</v>
       </c>
       <c r="D2" t="n">
-        <v>16.33025</v>
+        <v>16.13578</v>
       </c>
       <c r="E2" t="n">
-        <v>16.1443</v>
+        <v>16.5159</v>
       </c>
       <c r="F2" t="n">
-        <v>41.82156</v>
+        <v>42.07745</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05038</v>
+        <v>0.04862</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84166</v>
+        <v>1.77149</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.6769</v>
+        <v>16.58044</v>
       </c>
       <c r="D3" t="n">
-        <v>16.12517</v>
+        <v>16.21295</v>
       </c>
       <c r="E3" t="n">
-        <v>16.33553</v>
+        <v>16.40014</v>
       </c>
       <c r="F3" t="n">
-        <v>41.57112</v>
+        <v>41.8977</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05045</v>
+        <v>0.05014</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82485</v>
+        <v>1.81169</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.60866</v>
+        <v>16.33789</v>
       </c>
       <c r="D4" t="n">
-        <v>16.30835</v>
+        <v>16.25551</v>
       </c>
       <c r="E4" t="n">
-        <v>16.37965</v>
+        <v>16.32204</v>
       </c>
       <c r="F4" t="n">
-        <v>41.81966</v>
+        <v>42.55182</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05048</v>
+        <v>0.05045</v>
       </c>
       <c r="H4" t="n">
-        <v>1.77714</v>
+        <v>1.82588</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.39707</v>
+        <v>16.82821</v>
       </c>
       <c r="D5" t="n">
-        <v>15.85262</v>
+        <v>16.41252</v>
       </c>
       <c r="E5" t="n">
-        <v>16.64435</v>
+        <v>16.61122</v>
       </c>
       <c r="F5" t="n">
-        <v>42.32157</v>
+        <v>42.08406</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04997</v>
+        <v>0.0506</v>
       </c>
       <c r="H5" t="n">
-        <v>1.80538</v>
+        <v>1.77251</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.50934</v>
+        <v>16.94925</v>
       </c>
       <c r="D6" t="n">
-        <v>16.39069</v>
+        <v>16.69614</v>
       </c>
       <c r="E6" t="n">
-        <v>16.56901</v>
+        <v>16.79788</v>
       </c>
       <c r="F6" t="n">
-        <v>41.84839</v>
+        <v>42.11642</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0516</v>
+        <v>0.05166</v>
       </c>
       <c r="H6" t="n">
-        <v>1.82081</v>
+        <v>1.83733</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.00187</v>
+        <v>16.77481</v>
       </c>
       <c r="D7" t="n">
-        <v>16.64791</v>
+        <v>16.29833</v>
       </c>
       <c r="E7" t="n">
-        <v>16.52122</v>
+        <v>16.51013</v>
       </c>
       <c r="F7" t="n">
-        <v>41.82992</v>
+        <v>42.24384</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04882</v>
+        <v>0.04974</v>
       </c>
       <c r="H7" t="n">
-        <v>1.80551</v>
+        <v>1.82377</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.70447</v>
+        <v>16.78635</v>
       </c>
       <c r="D8" t="n">
-        <v>16.20435</v>
+        <v>16.5219</v>
       </c>
       <c r="E8" t="n">
-        <v>16.22299</v>
+        <v>16.65331</v>
       </c>
       <c r="F8" t="n">
-        <v>41.11482</v>
+        <v>41.86069</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04951</v>
+        <v>0.04918</v>
       </c>
       <c r="H8" t="n">
-        <v>1.78986</v>
+        <v>1.8231</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.67842</v>
+        <v>16.73029</v>
       </c>
       <c r="D9" t="n">
-        <v>16.60986</v>
+        <v>16.18526</v>
       </c>
       <c r="E9" t="n">
-        <v>16.43088</v>
+        <v>16.70523</v>
       </c>
       <c r="F9" t="n">
-        <v>41.27655</v>
+        <v>41.70527</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04872</v>
+        <v>0.04973</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8033</v>
+        <v>1.81109</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.76323</v>
+        <v>16.63588</v>
       </c>
       <c r="D10" t="n">
-        <v>16.38011</v>
+        <v>16.46036</v>
       </c>
       <c r="E10" t="n">
-        <v>16.37672</v>
+        <v>16.50678</v>
       </c>
       <c r="F10" t="n">
-        <v>41.71351</v>
+        <v>41.8344</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05054</v>
+        <v>0.04963</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8189</v>
+        <v>1.80152</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60386</v>
+        <v>0.59334</v>
       </c>
       <c r="D12" t="n">
-        <v>1.09359</v>
+        <v>1.10549</v>
       </c>
     </row>
     <row r="13">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.5896</v>
+        <v>0.60077</v>
       </c>
       <c r="D13" t="n">
-        <v>1.09321</v>
+        <v>1.1089</v>
       </c>
     </row>
     <row r="14">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.60438</v>
+        <v>0.59468</v>
       </c>
       <c r="D14" t="n">
-        <v>1.09374</v>
+        <v>1.10982</v>
       </c>
     </row>
     <row r="15">
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.59</v>
+        <v>0.60233</v>
       </c>
       <c r="D15" t="n">
-        <v>1.10269</v>
+        <v>1.09661</v>
       </c>
     </row>
     <row r="16">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.5986</v>
+        <v>0.5855</v>
       </c>
       <c r="D16" t="n">
-        <v>1.10514</v>
+        <v>1.11637</v>
       </c>
     </row>
     <row r="17">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.59222</v>
+        <v>0.60101</v>
       </c>
       <c r="D17" t="n">
-        <v>1.09795</v>
+        <v>1.06348</v>
       </c>
     </row>
     <row r="18">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.59474</v>
+        <v>0.60862</v>
       </c>
       <c r="D18" t="n">
-        <v>1.09806</v>
+        <v>1.10745</v>
       </c>
     </row>
     <row r="19">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.6025</v>
+        <v>0.59566</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0771</v>
+        <v>1.11331</v>
       </c>
     </row>
     <row r="20">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.60073</v>
+        <v>0.60865</v>
       </c>
       <c r="D20" t="n">
-        <v>1.10701</v>
+        <v>1.09977</v>
       </c>
     </row>
   </sheetData>
